--- a/Data/Results/Data_Cleaning_Audit.xlsx
+++ b/Data/Results/Data_Cleaning_Audit.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Cleaning Rules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'File Summary'!$A$1:$M$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Removed Rows'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'File Summary'!$A$1:$M$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Removed Rows'!$A$1:$M$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Speed Audit'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cleaning Rules'!$A$1:$F$13</definedName>
   </definedNames>
@@ -30,13 +30,16 @@
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -56,7 +59,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,13 +67,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46278.74056353728</v>
+        <v>46294.46676650071</v>
       </c>
     </row>
     <row r="3">
@@ -484,7 +493,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D:/TAT_MS_INTERCITY/Data/Input</t>
+          <t>D:/Hameeda_Projects/TAT_MS_INTERCITY/Data/Input</t>
         </is>
       </c>
     </row>
@@ -496,7 +505,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Data_Cleaning_Audit.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Data_Cleaning_Audit.xlsx</t>
         </is>
       </c>
     </row>
@@ -507,7 +516,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +526,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +556,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>30435</v>
+        <v>68274</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +576,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +586,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -607,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>30434</v>
+        <v>68257</v>
       </c>
     </row>
   </sheetData>
@@ -621,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -714,7 +723,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\05-07-2026\silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\05-07-2026\silkboard_to_madhuravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\10-07-2026\madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\10-07-2026\madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -812,7 +821,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\15-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\15-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -861,7 +870,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\15-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\15-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -910,7 +919,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\16-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\16-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -959,7 +968,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\16-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\16-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1008,7 +1017,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\17-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\17-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1057,7 +1066,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\17-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\17-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1106,7 +1115,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\18-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1155,7 +1164,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\18-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-07-2026\pondi_to_chennai_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1204,7 +1213,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1253,7 +1262,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1302,7 +1311,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\20-07-2026\pondi_to_chennai _ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-07-2026\pondi_to_chennai _ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1351,7 +1360,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\20-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-07-2026\pondi_to_chennai_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1400,7 +1409,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\20-07-2026\silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-07-2026\silkboard_to_maduravoyal_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1444,12 +1453,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\22-07-2026\madhuravoyal_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\28-07-2026\silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1468,7 +1477,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>344</v>
+        <v>1579</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -1486,19 +1495,19 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>344</v>
+        <v>1579</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
+          <t>avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\28-07-2026\silkboard_to_avr_roundana(salem)_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\29-07-2026\avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1517,7 +1526,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1579</v>
+        <v>1563</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -1535,19 +1544,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1579</v>
+        <v>1563</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\29-07-2026\avr_roundana(salem)_to_silkboard_ev_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\29-07-2026\silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1566,7 +1575,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1563</v>
+        <v>2704</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -1584,19 +1593,19 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1563</v>
+        <v>2704</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
+          <t>maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\29-07-2026\silkboard_to_maduravoyal_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\31-07-2026\maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1615,7 +1624,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2704</v>
+        <v>2666</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -1633,19 +1642,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2704</v>
+        <v>2666</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
+          <t>chennai_to_bangalore_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\31-07-2026\maduravoyal_to_silkboard_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\04-09-2026\chennai_to_bangalore_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1664,7 +1673,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2666</v>
+        <v>4448</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -1676,18 +1685,704 @@
         <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2666</v>
+        <v>4447</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\04-09-2026\maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1561</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\05-09-2026\silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3624</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>3623</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\05-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1179</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1178</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>913</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\11-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1355</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1354</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\11-09-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>4018</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\12-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\12-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>4051</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>4050</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-09-2026\maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>3865</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>3864</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>1343</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-09-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1286</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1286</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4014</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>4012</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>chennai_to_pondicherry_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\25-09-2026\chennai_to_pondicherry_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>2584</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>2584</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>2675</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>2675</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1698,10 +2393,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1711,7 +2406,7 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1791,7 +2486,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\19-07-2026\chennai_to_pondi_diesel_INTERCITY.xlsx</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1838,8 +2533,888 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>chennai_to_bangalore_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\04-09-2026\chennai_to_bangalore_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>46269.97703703704</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>13.06152</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>80.15842000000001</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>11.94444444444444</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Kanchipuram - Chennai Rd, Maduravoyal, Chennai, Tamil Nadu 600095, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\04-09-2026\maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>46270.25422453704</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>12.7782</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>77.77377</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Attibele, Karnataka 562107, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\04-09-2026\maduravoyal_to_silk_board_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>46270.36465277777</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>12.97098</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>77.60732</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Iris Business Hotel, Brigade Road, Arab Lines, Bengaluru, Bangalore North, Ashok Nagar, Karnataka, 560001, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\05-09-2026\silkboard_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3025</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>46271.15819444445</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>12.89685</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>79.80475</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>23.05555555555555</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Jambodai, Tamil Nadu 602108, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\05-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1168</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>46270.25422453704</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>12.7782</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>77.77377</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Attibele, Karnataka 562107, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>46271.07185185186</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>12.60995</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>78.09387</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>19.16666666666667</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Balagondarayanadurgam, Tamil Nadu 635122, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46271.11101851852</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>12.53795</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>78.37957</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Chinna mall patti, Krishnagiri - Ranipet Road (Old NH46), Bargur, Bargur, Tamil Nadu, 635104, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\06-09-2026\silkboard_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>46271.11251157407</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>12.53878</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>78.40487</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>21.94444444444444</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Oppathavadi, Tamil Nadu 635104, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\11-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>46277.14150462963</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>12.53625</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>78.40112000000001</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>24.16666666666666</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Oppathavadi, Tamil Nadu 635104, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\11-09-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3039</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>46277.19583333333</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>12.62727</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>78.07863</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>19.16666666666667</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Mallasandiram, Tamil Nadu 635117, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\12-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3464</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>46278.22534722222</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>12.89748</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>79.8057</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>23.05555555555555</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Jambodai, Tamil Nadu 602108, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-09-2026\maduravoyal_to_lalbag_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>46283.9567824074</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>12.53412</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>78.28619999999999</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>23.05555555555555</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Orappam, Tamil Nadu 635108, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>46283.92394675926</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>12.53455</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>78.39078000000001</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>21.94444444444444</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Anginayakkan Palli, Bargur - Tirupattur Road, Bargur, Bargur, Tamil Nadu, 635104, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\18-09-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>917</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>46283.93224537037</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>12.53407</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>78.29246999999999</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>19.72222222222222</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Sundampatti, Orappam, Tamil Nadu 635108, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>46285.57486111111</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>12.5377</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>78.38005</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>22.22222222222222</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Chennai - Bengaluru Hwy, Oppathavadi, Tamil Nadu 635104, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\20-09-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3706</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>46285.74173611111</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>13.02253</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>80.01793000000001</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>13.88888888888889</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Perumalpattu - Kottamedu Rd, Kuthambakkam, Tamil Nadu 600124, India</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Data/Results/Data_Cleaning_Audit.xlsx
+++ b/Data/Results/Data_Cleaning_Audit.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Cleaning Rules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'File Summary'!$A$1:$M$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Removed Rows'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'File Summary'!$A$1:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Removed Rows'!$A$1:$M$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Speed Audit'!$A$1:$N$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cleaning Rules'!$A$1:$F$13</definedName>
   </definedNames>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46294.46676650071</v>
+        <v>46301.96813307998</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>68274</v>
+        <v>80689</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>68257</v>
+        <v>80668</v>
       </c>
     </row>
   </sheetData>
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
@@ -2286,12 +2286,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>chennai_to_pondicherry_ev_intercity.xlsx</t>
+          <t>chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\25-09-2026\chennai_to_pondicherry_ev_intercity.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\25-09-2026\chennai_to_pondicherry_diesel_intercity.xlsx</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2584</v>
+        <v>958</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
@@ -2322,67 +2322,361 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2584</v>
+        <v>957</v>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>chennai_to_pondicherry_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\25-09-2026\chennai_to_pondicherry_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>2584</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>2584</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>pondicherry_to_chennai_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\26-09-2026\pondicherry_to_chennai_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>973</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>973</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>pondicherry_to_chennai_ev_intercity.xlsx</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\26-09-2026\pondicherry_to_chennai_ev_intercity.xlsx</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>DEVICE_RAW</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>CLEANED</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>2675</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="n">
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>2675</v>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1344</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1342</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\02-10-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>3632</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>3631</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\03-10-2026\madiwala_to_maduravoyal_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\03-10-2026\madiwala_to_maduravoyal_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>4237</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>4237</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M35"/>
+  <autoFilter ref="A1:M41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2393,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3413,8 +3707,228 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>chennai_to_pondicherry_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\25-09-2026\chennai_to_pondicherry_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>46290.81975694445</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>11.93717</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>79.81885</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Thiruvalluvar Road, Sithankudi, Oulgaret, Ozhukarai Taluk, Brindavanam, Puducherry, 605013, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1157</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>46298.17877314815</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>12.77718</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>77.77607</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Attibele, Karnataka 562107, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\02-10-2026\maduravoyal_to_madiwala_diesel_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1344</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>46298.22202546296</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>12.96495</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>77.59851999999999</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Thales, Richmond Road, Langford Gardens, Bengaluru, Bangalore North, Richmond Town, Karnataka, 560001, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Input\02-10-2026\maduravoyal_to_madiwala_ev_intercity.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DEVICE_RAW</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2769</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>DUPLICATE_REMOVAL</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Exact duplicate of an earlier standardized telemetry row; first occurrence retained</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>46298.17090277778</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>12.6264</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>78.07932</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Chennekothapalli Rd, Mallasandiram, Tamil Nadu 635117, India</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
